--- a/Excel/Vertical/perbandingan_Jumlah Belok.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Belok.xlsx
@@ -545,10 +545,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0.5</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -568,10 +568,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0.4166666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -591,10 +591,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>0.6111111111111112</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -614,10 +614,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>0.75</v>
+        <v>0.71875</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -683,10 +683,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>0.4090909090909091</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -706,10 +706,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>0.5</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -729,10 +729,10 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -798,10 +798,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>0.7142857142857143</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -821,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -844,10 +844,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -867,10 +867,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>0.8333333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -890,10 +890,10 @@
         <v>11</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>0.9047619047619048</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>

--- a/Excel/Vertical/perbandingan_Jumlah Belok.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Belok.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Naik</t>
   </si>
 </sst>
 </file>
@@ -449,6 +452,12 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -466,6 +475,12 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -483,6 +498,12 @@
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -500,6 +521,12 @@
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -517,8 +544,14 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -534,8 +567,14 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>0.1666666666666667</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -551,8 +590,14 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>16</v>
+      </c>
+      <c r="F8">
+        <v>0.1111111111111111</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -568,8 +613,14 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>0.3125</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -585,6 +636,12 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
       <c r="G10" t="s">
         <v>12</v>
       </c>
@@ -602,8 +659,14 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>0.125</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -619,8 +682,14 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>0.4545454545454545</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -636,8 +705,14 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>0.4615384615384616</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -653,8 +728,14 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -670,8 +751,14 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>0.5</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -687,8 +774,14 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>0.65</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -704,8 +797,14 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>0.75</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -721,8 +820,14 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>0.2</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -738,8 +843,14 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -755,8 +866,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>0.7916666666666666</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -772,8 +889,14 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>0.8809523809523809</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Jumlah Belok.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Belok.xlsx
@@ -568,10 +568,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -591,10 +591,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>0.1111111111111111</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -614,10 +614,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>0.3125</v>
+        <v>0.59375</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -821,13 +821,13 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -844,10 +844,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
